--- a/OrgIt_Master_Bulk_SAMPLE.xlsx
+++ b/OrgIt_Master_Bulk_SAMPLE.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="262">
   <si>
     <t>OrgIt Master Bulk workbook — fill in this order:</t>
   </si>
@@ -808,9 +808,6 @@
   </si>
   <si>
     <t>one_time</t>
-  </si>
-  <si>
-    <t>+919876543213</t>
   </si>
   <si>
     <t>5000</t>
@@ -33137,25 +33134,25 @@
         <v>191</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K2" t="s">
         <v>254</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>255</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>256</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>257</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>258</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>259</v>
-      </c>
-      <c r="P2" t="s">
-        <v>260</v>
       </c>
       <c r="Q2" t="s">
         <v>2</v>
@@ -33164,10 +33161,10 @@
         <v>2</v>
       </c>
       <c r="S2" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" t="s">
         <v>261</v>
-      </c>
-      <c r="T2" t="s">
-        <v>262</v>
       </c>
       <c r="U2" t="s">
         <v>2</v>
